--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JagalchiHang\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3456EE12-56A7-4133-9DB3-41BDFCCF896A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4268705E-6B3D-40A5-820A-8F475C0B5BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3165" yWindow="1635" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="시트1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
   <si>
     <t>Crob item</t>
   </si>
@@ -71,18 +71,12 @@
     <t>씬에 배치할 프리팹 경로</t>
   </si>
   <si>
-    <t>id</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
@@ -116,9 +110,6 @@
     <t>PrefebPath</t>
   </si>
   <si>
-    <t>작물 아이템 1 설명</t>
-  </si>
-  <si>
     <t>SeedItem1</t>
   </si>
   <si>
@@ -193,13 +184,97 @@
   <si>
     <t>Crob_item6</t>
     <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Id</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>작물</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아이템</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>설명</t>
+    </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Name</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이디</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crob_item2</t>
+  </si>
+  <si>
+    <t>Crob_item3</t>
+  </si>
+  <si>
+    <t>Crob_item4</t>
+  </si>
+  <si>
+    <t>Crob_item5</t>
+  </si>
+  <si>
+    <t>Crob_item6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -234,6 +309,35 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -255,7 +359,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -263,6 +367,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -481,325 +590,352 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" customWidth="1"/>
-    <col min="9" max="10" width="19.7109375" customWidth="1"/>
-    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="2" max="2" width="16.5703125" customWidth="1"/>
+    <col min="3" max="3" width="25.28515625" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="19.42578125" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="10" max="11" width="19.7109375" customWidth="1"/>
+    <col min="13" max="13" width="17.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" ht="15.75" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:13" ht="14.25">
+      <c r="A2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="str">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="1" t="str">
         <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("AI(""표 컨텍스트를 기반으로 이 셀에 적절한 값을 입력해 줘"")"),"int")</f>
         <v>int</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:13">
+      <c r="A3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K3" s="2" t="s">
+    </row>
+    <row r="4" spans="1:13" ht="14.25">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="G4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" s="4">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2">
+        <v>10</v>
+      </c>
+      <c r="J4" s="2">
+        <v>3</v>
+      </c>
+      <c r="K4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="14.25">
+      <c r="A5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="1">
+        <v>2</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="G5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="4">
-        <v>2</v>
-      </c>
-      <c r="H4" s="2">
-        <v>10</v>
-      </c>
-      <c r="I4" s="2">
-        <v>3</v>
-      </c>
-      <c r="J4" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>2</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="4">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2">
+      <c r="H5" s="4">
+        <v>3</v>
+      </c>
+      <c r="I5" s="2">
         <v>20</v>
-      </c>
-      <c r="I5" s="2">
-        <v>4</v>
       </c>
       <c r="J5" s="2">
         <v>4</v>
       </c>
+      <c r="K5" s="2">
+        <v>4</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="14.25">
       <c r="A6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1">
+        <v>3</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" s="4">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>10</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="14.25">
+      <c r="A7" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1">
+        <v>3</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H7" s="4">
+        <v>3</v>
+      </c>
+      <c r="I7" s="2">
+        <v>20</v>
+      </c>
+      <c r="J7" s="2">
+        <v>2</v>
+      </c>
+      <c r="K7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="14.25">
+      <c r="A8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="2">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>20</v>
+      </c>
+      <c r="J8" s="2">
+        <v>4</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="14.25">
+      <c r="A9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1">
-        <v>3</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="4">
-        <v>3</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="C9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2">
+        <v>2</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="2">
+        <v>3</v>
+      </c>
+      <c r="I9" s="2">
         <v>10</v>
       </c>
-      <c r="I6" s="2">
-        <v>2</v>
-      </c>
-      <c r="J6" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="4">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2">
-        <v>20</v>
-      </c>
-      <c r="I7" s="2">
-        <v>2</v>
-      </c>
-      <c r="J7" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="2">
-        <v>4</v>
-      </c>
-      <c r="D8" s="2">
-        <v>2</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="2">
-        <v>2</v>
-      </c>
-      <c r="H8" s="2">
-        <v>20</v>
-      </c>
-      <c r="I8" s="2">
-        <v>4</v>
-      </c>
-      <c r="J8" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="2">
-        <v>3</v>
-      </c>
-      <c r="D9" s="2">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="2">
-        <v>3</v>
-      </c>
-      <c r="H9" s="2">
-        <v>10</v>
-      </c>
-      <c r="I9" s="2">
-        <v>2</v>
-      </c>
       <c r="J9" s="2">
+        <v>2</v>
+      </c>
+      <c r="K9" s="2">
         <v>2</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -16,103 +16,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
   <x:si>
-    <x:t>HarvestItem4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrowthTimeSeconds</x:t>
-  </x:si>
-  <x:si>
     <x:t>성장 단계별 걸리는 시간 (분 단위)</x:t>
   </x:si>
   <x:si>
-    <x:t>수확시 씨앗 최소 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씬에 배치할 프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 얻는 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최소 획득개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crob_item5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crob_item1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crob_item3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crob_item4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crob_item6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crob_item2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 6설명</x:t>
+    <x:t>GrowthStageMinutesList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:r>
@@ -157,67 +67,157 @@
     </x:r>
   </x:si>
   <x:si>
+    <x:t>Crob item</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물 아이템 3 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물 아이템 5설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItem4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItem2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물 아이템 2설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItem3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물 아이템 4 설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItem1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>Crob item</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 3 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 4 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 5설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 2설명</x:t>
+    <x:t>HarvestItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물 아이템 6설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crob_item1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crob_item4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crob_item5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItem6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crob_item2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crob_item3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItem5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crob_item6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItem5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItem4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬에 배치할 프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItem1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItem2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 얻는 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최소 획득개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최소 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItem3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItem6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,3,3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,3,1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,3,1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,2,3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,2,2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물설명</x:t>
   </x:si>
   <x:si>
     <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,2,2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,3,1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,2,3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,3,3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,3,1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1052,140 +1052,140 @@
   <x:sheetData>
     <x:row r="1" spans="1:13" customHeight="1">
       <x:c r="A1" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H1" s="3" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J1" s="2" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="K1" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="L1" s="2" t="s">
         <x:v>35</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="H1" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="J1" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="K1" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="L1" s="2" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="M1" s="2"/>
     </x:row>
     <x:row r="2" spans="1:13" ht="13.75">
       <x:c r="A2" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G2" s="1" t="str">
         <x:f>IFERROR(__xludf.DUMMYFUNCTION("AI(""표 컨텍스트를 기반으로 이 셀에 적절한 값을 입력해 줘"")"),"int")</x:f>
         <x:v>int</x:v>
       </x:c>
       <x:c r="H2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="K2" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="L2" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="M2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:13" ht="16.399999999999999">
       <x:c r="A3" s="5" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
       <x:c r="F3" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="H3" s="2" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="J3" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="K3" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="L3" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="M3" s="2"/>
     </x:row>
     <x:row r="4" spans="1:10" ht="13.75">
       <x:c r="A4" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C4" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G4" s="4">
         <x:v>2</x:v>
@@ -1202,22 +1202,22 @@
     </x:row>
     <x:row r="5" spans="1:10" ht="13.75">
       <x:c r="A5" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G5" s="4">
         <x:v>3</x:v>
@@ -1234,22 +1234,22 @@
     </x:row>
     <x:row r="6" spans="1:10" ht="13.75">
       <x:c r="A6" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G6" s="4">
         <x:v>3</x:v>
@@ -1266,22 +1266,22 @@
     </x:row>
     <x:row r="7" spans="1:10" ht="13.75">
       <x:c r="A7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G7" s="4">
         <x:v>3</x:v>
@@ -1298,22 +1298,22 @@
     </x:row>
     <x:row r="8" spans="1:10" ht="13.75">
       <x:c r="A8" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G8" s="2">
         <x:v>2</x:v>
@@ -1330,22 +1330,22 @@
     </x:row>
     <x:row r="9" spans="1:10" ht="13.75">
       <x:c r="A9" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G9" s="2">
         <x:v>3</x:v>
@@ -1361,7 +1361,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="0" fitToHeight="0" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <x:si>
     <x:t>성장 단계별 걸리는 시간 (분 단위)</x:t>
   </x:si>
@@ -196,22 +196,7 @@
     <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>2,3,3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,3,1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,3,1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,2,3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,2,2</x:t>
   </x:si>
   <x:si>
     <x:t>작물설명</x:t>
@@ -350,7 +335,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="11">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -376,6 +361,12 @@
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -1058,7 +1049,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
         <x:v>0</x:v>
@@ -1082,7 +1073,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="K1" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="L1" s="2" t="s">
         <x:v>35</x:v>
@@ -1134,7 +1125,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>13</x:v>
@@ -1178,8 +1169,8 @@
       <x:c r="C4" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>50</x:v>
+      <x:c r="D4" s="10">
+        <x:v>120130120</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
         <x:v>12</x:v>
@@ -1210,8 +1201,8 @@
       <x:c r="C5" s="4" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>52</x:v>
+      <x:c r="D5" s="10">
+        <x:v>140120140</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>8</x:v>
@@ -1242,8 +1233,8 @@
       <x:c r="C6" s="4" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>47</x:v>
+      <x:c r="D6" s="10">
+        <x:v>120180120</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>10</x:v>
@@ -1274,8 +1265,8 @@
       <x:c r="C7" s="4" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>51</x:v>
+      <x:c r="D7" s="10">
+        <x:v>120160140</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>7</x:v>
@@ -1306,8 +1297,8 @@
       <x:c r="C8" s="4" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D8" s="2" t="s">
-        <x:v>48</x:v>
+      <x:c r="D8" s="9">
+        <x:v>120140150</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>25</x:v>
@@ -1338,8 +1329,8 @@
       <x:c r="C9" s="4" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D9" s="2" t="s">
-        <x:v>52</x:v>
+      <x:c r="D9" s="9">
+        <x:v>120130140</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>22</x:v>

--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17820"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294938660" windowHeight="16530"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -19,210 +19,228 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="74">
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3456,2304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Crop</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9504,6336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4320,2880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop Item</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매운 양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포슬포슬 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMinCount</x:t>
+  </x:si>
   <x:si>
     <x:t>SeedDropMaxCount</x:t>
   </x:si>
   <x:si>
+    <x:t>576,2304,2304,576</x:t>
+  </x:si>
+  <x:si>
     <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
   </x:si>
   <x:si>
-    <x:t>SeedDropMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItemDataId</x:t>
+    <x:t>수확시 얻는 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>864,2592,864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1440,4320,1440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최대 획득 개수</x:t>
   </x:si>
   <x:si>
     <x:t>HarvestMaxCount</x:t>
   </x:si>
   <x:si>
-    <x:t>HarvestItem2</x:t>
+    <x:t>SeedItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬에 배치할 프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최소 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1152,3456,1152</x:t>
   </x:si>
   <x:si>
     <x:t>수확시 작물 최소 획득개수</x:t>
   </x:si>
   <x:si>
-    <x:t>수확시 얻는 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씬에 배치할 프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItem1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최소 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_item5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60,120,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60,120,30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_item6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_item2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_item1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_item4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30,120,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 2설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_item3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 3 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop item</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 6설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 5설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물 아이템 4 설명</x:t>
-  </x:si>
-  <x:si>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>작물</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="Arial"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>아이템</x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="Arial"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t xml:space="preserve"> 1 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:rFont val="맑은 고딕"/>
-        <x:sz val="10"/>
-        <x:color rgb="ff000000"/>
-      </x:rPr>
-      <x:t>설명</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>120,180,60</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItem1</x:t>
+    <x:t>달달한 당근. 씨앗으로 당근씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토. 씨앗으로 토마토씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박. 씨앗으로 호박씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrowthStageMinutesList</x:t>
   </x:si>
   <x:si>
     <x:t>성장 단계별 걸리는 시간 (분 단위)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrowthStageMinutesList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -310,7 +328,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="12">
+  <x:cellXfs count="13">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -332,19 +353,19 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="top"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="top"/>
     </x:xf>
-    <x:xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <x:xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -943,328 +964,396 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:M9"/>
+  <x:dimension ref="A1:M11"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
-    <x:col min="2" max="2" width="16.5703125" style="1" customWidth="1"/>
-    <x:col min="3" max="3" width="25.28515625" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="32.3125" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="29.7265625" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="6" max="6" width="24.7109375" style="1" customWidth="1"/>
-    <x:col min="7" max="7" width="20" style="1" customWidth="1"/>
-    <x:col min="8" max="9" width="25.4453125" style="1" customWidth="1"/>
-    <x:col min="10" max="11" width="19.7109375" style="1" customWidth="1"/>
-    <x:col min="13" max="13" width="17.7109375" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="14.28515625" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="16.5703125" style="2" customWidth="1"/>
+    <x:col min="3" max="3" width="45.25" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="32.3125" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="24.7109375" style="2" customWidth="1"/>
+    <x:col min="7" max="7" width="20" style="2" customWidth="1"/>
+    <x:col min="8" max="9" width="25.4453125" style="2" customWidth="1"/>
+    <x:col min="10" max="11" width="19.7109375" style="2" customWidth="1"/>
+    <x:col min="13" max="13" width="17.7109375" style="2" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:13" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C1" s="3" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H1" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="I1" s="3" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J1" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K1" s="3" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="L1" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="M1" s="3"/>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B1" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C1" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E1" s="3" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F1" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="G1" s="3" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H1" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="J1" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="K1" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="L1" s="4" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="M1" s="4"/>
     </x:row>
     <x:row r="2" spans="1:13" ht="13.550000000000001">
-      <x:c r="A2" s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D2" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E2" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F2" s="2" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="str">
+      <x:c r="A2" s="7" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B2" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C2" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E2" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="F2" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G2" s="3" t="str">
         <x:f>IFERROR(__xludf.DUMMYFUNCTION("AI(""표 컨텍스트를 기반으로 이 셀에 적절한 값을 입력해 줘"")"),"int")</x:f>
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H2" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I2" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="J2" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="K2" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="L2" s="3" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="M2" s="3"/>
+      <x:c r="H2" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="I2" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="J2" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="K2" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="L2" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="M2" s="4"/>
     </x:row>
     <x:row r="3" spans="1:13" ht="16.399999999999999">
-      <x:c r="A3" s="6" t="s">
-        <x:v>19</x:v>
+      <x:c r="A3" s="7" t="s">
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B3" s="9" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D3" s="2" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C3" s="3" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="3" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E3" s="3" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F3" s="3" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H3" s="4" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I3" s="4" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="J3" s="4" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K3" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L3" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="M3" s="4"/>
+    </x:row>
+    <x:row r="4" spans="1:11" ht="13.550000000000001">
+      <x:c r="A4" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E4" s="3" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="G3" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="H3" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="I3" s="3" t="s">
+      <x:c r="G4" s="6">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H4" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I4" s="4">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J3" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K3" s="3" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="L3" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="M3" s="3"/>
-    </x:row>
-    <x:row r="4" spans="1:10" ht="13.550000000000001">
-      <x:c r="A4" s="5" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B4" s="5" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C4" s="7" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D4" s="10" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E4" s="2" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F4" s="5" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G4" s="5">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H4" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I4" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J4" s="3">
-        <x:v>10</x:v>
+      <x:c r="J4" s="4">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="K4" s="2" t="s">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:10" ht="13.550000000000001">
-      <x:c r="A5" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D5" s="10" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="E5" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F5" s="5" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G5" s="5">
+      <x:c r="A5" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G5" s="6">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H5" s="3">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I5" s="3">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J5" s="3">
-        <x:v>20</x:v>
+      <x:c r="H5" s="4">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="I5" s="4">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J5" s="4">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:10" ht="13.550000000000001">
-      <x:c r="A6" s="5" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="D6" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E6" s="2" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F6" s="5" t="s">
+      <x:c r="A6" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E6" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G6" s="6">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H6" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I6" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J6" s="4">
         <x:v>14</x:v>
-      </x:c>
-      <x:c r="G6" s="5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H6" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="I6" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J6" s="3">
-        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10" ht="13.550000000000001">
-      <x:c r="A7" s="5" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="B7" s="5" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C7" s="5" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D7" s="10" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F7" s="5" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G7" s="5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H7" s="3">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I7" s="3">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J7" s="3">
+      <x:c r="A7" s="6" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E7" s="3" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G7" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H7" s="4">
         <x:v>30</x:v>
+      </x:c>
+      <x:c r="I7" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J7" s="4">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10" ht="13.550000000000001">
-      <x:c r="A8" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B8" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D8" s="10" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="E8" s="2" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F8" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G8" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H8" s="3">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="I8" s="3">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J8" s="3">
-        <x:v>20</x:v>
+      <x:c r="A8" s="6" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D8" s="12" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E8" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G8" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H8" s="4">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="I8" s="4">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="4">
+        <x:v>5</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10" ht="13.550000000000001">
-      <x:c r="A9" s="5" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="B9" s="5" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="s">
+      <x:c r="A9" s="6" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="G9" s="4">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H9" s="4">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I9" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="J9" s="4">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:10" customHeight="1">
+      <x:c r="A10" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C10" s="2" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D10" s="12" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G10" s="2">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H10" s="2">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I10" s="2">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="J10" s="2">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:10" customHeight="1">
+      <x:c r="A11" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C11" s="2" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D9" s="11">
-        <x:v>60120120</x:v>
-      </x:c>
-      <x:c r="E9" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="F9" s="5" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G9" s="3">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H9" s="3">
+      <x:c r="D11" s="12" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G11" s="2">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H11" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I11" s="2">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="J11" s="2">
         <x:v>10</x:v>
-      </x:c>
-      <x:c r="I9" s="3">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J9" s="3">
-        <x:v>30</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294938660" windowHeight="16530"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17820"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -19,75 +19,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="74">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
+  <x:si>
+    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>576,2304,2304,576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매운 양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포슬포슬 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Wheat</x:t>
+  </x:si>
   <x:si>
     <x:t>Crop_Wheat</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Wheat</x:t>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Crop</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9504,6336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot</x:t>
   </x:si>
   <x:si>
     <x:t>3456,2304</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Crop</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9504,6336</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4320,2880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop Item</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4320,2880</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop Item</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
   </x:si>
   <x:si>
     <x:t>int</x:t>
@@ -99,145 +174,70 @@
     <x:t>Pea</x:t>
   </x:si>
   <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매운 양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포슬포슬 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>576,2304,2304,576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1440,4320,1440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>864,2592,864</x:t>
   </x:si>
   <x:si>
     <x:t>수확시 얻는 아이템 id</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
+    <x:t>수확시 씨앗 최대 획득 개수</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Seed_Pea</x:t>
   </x:si>
   <x:si>
-    <x:t>864,2592,864</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1440,4320,1440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMaxCount</x:t>
-  </x:si>
-  <x:si>
     <x:t>SeedItemDataId</x:t>
   </x:si>
   <x:si>
     <x:t>씬에 배치할 프리팹 경로</x:t>
   </x:si>
   <x:si>
+    <x:t>수확시 작물 최소 획득개수</x:t>
+  </x:si>
+  <x:si>
     <x:t>수확시 씨앗 최소 획득 개수</x:t>
   </x:si>
   <x:si>
     <x:t>1152,3456,1152</x:t>
   </x:si>
   <x:si>
-    <x:t>수확시 작물 최소 획득개수</x:t>
-  </x:si>
-  <x:si>
     <x:t>달달한 당근. 씨앗으로 당근씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>토마토. 씨앗으로 토마토씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
+    <x:t>GrowthStageMinutesList</x:t>
+  </x:si>
+  <x:si>
     <x:t>호박. 씨앗으로 호박씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrowthStageMinutesList</x:t>
   </x:si>
   <x:si>
     <x:t>성장 단계별 걸리는 시간 (분 단위)</x:t>
@@ -976,42 +976,43 @@
     <x:col min="7" max="7" width="20" style="2" customWidth="1"/>
     <x:col min="8" max="9" width="25.4453125" style="2" customWidth="1"/>
     <x:col min="10" max="11" width="19.7109375" style="2" customWidth="1"/>
+    <x:col min="12" max="12" width="21.6953125" bestFit="1" customWidth="1"/>
     <x:col min="13" max="13" width="17.7109375" style="2" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:13" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B1" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C1" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
         <x:v>73</x:v>
       </x:c>
       <x:c r="E1" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F1" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G1" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H1" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I1" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="J1" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
       <x:c r="K1" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="L1" s="4" t="s">
         <x:v>65</x:v>
@@ -1020,101 +1021,101 @@
     </x:row>
     <x:row r="2" spans="1:13" ht="13.550000000000001">
       <x:c r="A2" s="7" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B2" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C2" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E2" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F2" s="3" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G2" s="3" t="str">
         <x:f>IFERROR(__xludf.DUMMYFUNCTION("AI(""표 컨텍스트를 기반으로 이 셀에 적절한 값을 입력해 줘"")"),"int")</x:f>
         <x:v>int</x:v>
       </x:c>
       <x:c r="H2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="J2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="K2" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="L2" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="M2" s="4"/>
     </x:row>
     <x:row r="3" spans="1:13" ht="16.399999999999999">
       <x:c r="A3" s="7" t="s">
-        <x:v>24</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B3" s="9" t="s">
-        <x:v>34</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D3" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E3" s="3" t="s">
         <x:v>64</x:v>
       </x:c>
       <x:c r="F3" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="3" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H3" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I3" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="J3" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K3" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="L3" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="M3" s="4"/>
     </x:row>
-    <x:row r="4" spans="1:11" ht="13.550000000000001">
+    <x:row r="4" spans="1:12" ht="13.550000000000001">
       <x:c r="A4" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="6" t="s">
-        <x:v>38</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C4" s="10" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E4" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G4" s="6">
         <x:v>3</x:v>
@@ -1129,27 +1130,30 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K4" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="L4" t="s">
+        <x:v>38</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" spans="1:10" ht="13.550000000000001">
+    <x:row r="5" spans="1:12" ht="13.550000000000001">
       <x:c r="A5" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C5" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E5" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F5" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G5" s="6">
         <x:v>3</x:v>
@@ -1163,25 +1167,28 @@
       <x:c r="J5" s="4">
         <x:v>13</x:v>
       </x:c>
+      <x:c r="L5" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
     </x:row>
-    <x:row r="6" spans="1:10" ht="13.550000000000001">
+    <x:row r="6" spans="1:12" ht="13.550000000000001">
       <x:c r="A6" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D6" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="F6" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G6" s="6">
         <x:v>2</x:v>
@@ -1195,25 +1202,28 @@
       <x:c r="J6" s="4">
         <x:v>14</x:v>
       </x:c>
+      <x:c r="L6" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
     </x:row>
-    <x:row r="7" spans="1:10" ht="13.550000000000001">
+    <x:row r="7" spans="1:12" ht="13.550000000000001">
       <x:c r="A7" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C7" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D7" s="11" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E7" s="3" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F7" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G7" s="6">
         <x:v>10</x:v>
@@ -1227,25 +1237,28 @@
       <x:c r="J7" s="4">
         <x:v>15</x:v>
       </x:c>
+      <x:c r="L7" s="6" t="s">
+        <x:v>28</x:v>
+      </x:c>
     </x:row>
-    <x:row r="8" spans="1:10" ht="13.550000000000001">
+    <x:row r="8" spans="1:12" ht="13.550000000000001">
       <x:c r="A8" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E8" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F8" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="G8" s="4">
         <x:v>5</x:v>
@@ -1259,25 +1272,28 @@
       <x:c r="J8" s="4">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="L8" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
     </x:row>
-    <x:row r="9" spans="1:10" ht="13.550000000000001">
+    <x:row r="9" spans="1:12" ht="13.550000000000001">
       <x:c r="A9" s="6" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D9" s="12" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E9" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E9" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="F9" s="6" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="G9" s="4">
         <x:v>2</x:v>
@@ -1291,25 +1307,28 @@
       <x:c r="J9" s="4">
         <x:v>21</x:v>
       </x:c>
+      <x:c r="L9" s="6" t="s">
+        <x:v>57</x:v>
+      </x:c>
     </x:row>
-    <x:row r="10" spans="1:10" customHeight="1">
+    <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="2" t="s">
         <x:v>70</x:v>
       </x:c>
       <x:c r="D10" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E10" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F10" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G10" s="2">
         <x:v>4</x:v>
@@ -1323,25 +1342,28 @@
       <x:c r="J10" s="2">
         <x:v>10</x:v>
       </x:c>
+      <x:c r="L10" t="s">
+        <x:v>40</x:v>
+      </x:c>
     </x:row>
-    <x:row r="11" spans="1:10" customHeight="1">
+    <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C11" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D11" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F11" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="G11" s="2">
         <x:v>6</x:v>
@@ -1354,6 +1376,9 @@
       </x:c>
       <x:c r="J11" s="2">
         <x:v>10</x:v>
+      </x:c>
+      <x:c r="L11" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17820"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17805"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>

--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17805"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17820"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -19,137 +19,158 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="74">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
+  <x:si>
+    <x:t>성장 단계별 걸리는 시간 (분 단위) 864,2592,864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72,144,144</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>576,2304,2304,576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
   <x:si>
     <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
-    <x:t>HarvestItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>576,2304,2304,576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
     <x:t>Pumpkin</x:t>
   </x:si>
   <x:si>
+    <x:t>Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포슬포슬 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매운 양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
     <x:t>Onion</x:t>
   </x:si>
   <x:si>
-    <x:t>작물설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매운 양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포슬포슬 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tomato</x:t>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon_Crop</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9504,6336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Wheat</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3456,2304</x:t>
+  </x:si>
+  <x:si>
     <x:t>Crop_Wheat</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Crop</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9504,6336</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3456,2304</x:t>
+    <x:t>Item_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4320,2880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pea</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4320,2880</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Onion</x:t>
+    <x:t>Crop_Carrot</x:t>
   </x:si>
   <x:si>
     <x:t>Crop_Potato</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Tomato</x:t>
-  </x:si>
-  <x:si>
     <x:t>Crop_Tomato</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn</x:t>
-  </x:si>
-  <x:si>
     <x:t>Crop Item</x:t>
   </x:si>
   <x:si>
@@ -159,88 +180,70 @@
     <x:t>PrefabPath</x:t>
   </x:si>
   <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pea</x:t>
+    <x:t>수확시 씨앗 최소 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최소 획득개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>864,2592,864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 얻는 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬에 배치할 프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1152,3456,1152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Pumpkin</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Seed_Corn</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
     <x:t>HarvestMinCount</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
     <x:t>수확시 작물 최대 획득 개수</x:t>
   </x:si>
   <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
     <x:t>1440,4320,1440</x:t>
   </x:si>
   <x:si>
     <x:t>HarvestMaxCount</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>864,2592,864</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 얻는 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씬에 배치할 프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최소 획득개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최소 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1152,3456,1152</x:t>
+    <x:t>토마토. 씨앗으로 토마토씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>달달한 당근. 씨앗으로 당근씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
-    <x:t>토마토. 씨앗으로 토마토씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
     <x:t>GrowthStageMinutesList</x:t>
   </x:si>
   <x:si>
     <x:t>호박. 씨앗으로 호박씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성장 단계별 걸리는 시간 (분 단위)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -328,7 +331,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -967,418 +973,418 @@
   <x:dimension ref="A1:M11"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.28515625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="16.5703125" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="45.25" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="32.3125" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="29.7265625" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="6" max="6" width="24.7109375" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="20" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="25.4453125" style="2" customWidth="1"/>
-    <x:col min="10" max="11" width="19.7109375" style="2" customWidth="1"/>
-    <x:col min="12" max="12" width="21.6953125" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="13" width="17.7109375" style="2" customWidth="1"/>
+    <x:col min="1" max="1" width="14.28515625" style="2" customWidth="1"/>
+    <x:col min="2" max="2" width="16.5703125" style="3" customWidth="1"/>
+    <x:col min="3" max="3" width="45.25" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="49.8984375" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="29.7265625" style="3" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="24.7109375" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="20" style="3" customWidth="1"/>
+    <x:col min="8" max="9" width="25.4453125" style="3" customWidth="1"/>
+    <x:col min="10" max="11" width="19.7109375" style="3" customWidth="1"/>
+    <x:col min="12" max="12" width="21.6953125" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="13" width="17.7109375" style="3" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:13" customHeight="1">
-      <x:c r="A1" s="8" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C1" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D1" s="3" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E1" s="3" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F1" s="3" t="s">
+      <x:c r="A1" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B1" s="4" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C1" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D1" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F1" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G1" s="4" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H1" s="6" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I1" s="5" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="J1" s="5" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="K1" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L1" s="5" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="G1" s="3" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H1" s="5" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I1" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="J1" s="4" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K1" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L1" s="4" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="M1" s="4"/>
+      <x:c r="M1" s="5"/>
     </x:row>
     <x:row r="2" spans="1:13" ht="13.550000000000001">
-      <x:c r="A2" s="7" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B2" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C2" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D2" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E2" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F2" s="3" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G2" s="3" t="str">
+      <x:c r="A2" s="8" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D2" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E2" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G2" s="4" t="str">
         <x:f>IFERROR(__xludf.DUMMYFUNCTION("AI(""표 컨텍스트를 기반으로 이 셀에 적절한 값을 입력해 줘"")"),"int")</x:f>
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H2" s="4" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="I2" s="4" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="J2" s="4" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="K2" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="L2" s="4" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="M2" s="4"/>
+      <x:c r="H2" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="I2" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J2" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="K2" s="5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="L2" s="5" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="M2" s="5"/>
     </x:row>
     <x:row r="3" spans="1:13" ht="16.399999999999999">
-      <x:c r="A3" s="7" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B3" s="9" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C3" s="3" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D3" s="3" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E3" s="3" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
+      <x:c r="A3" s="8" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I3" s="5" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J3" s="5" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K3" s="5" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L3" s="5" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="H3" s="4" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="I3" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J3" s="4" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="K3" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="L3" s="4" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="M3" s="4"/>
+      <x:c r="M3" s="5"/>
     </x:row>
     <x:row r="4" spans="1:12" ht="13.550000000000001">
-      <x:c r="A4" s="6" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C4" s="10" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E4" s="3" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F4" s="6" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G4" s="6">
+      <x:c r="A4" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B4" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="D4" s="12" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F4" s="7" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G4" s="7">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H4" s="4">
+      <x:c r="H4" s="5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I4" s="4">
+      <x:c r="I4" s="5">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J4" s="4">
+      <x:c r="J4" s="5">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K4" s="2" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="L4" t="s">
-        <x:v>38</x:v>
+      <x:c r="K4" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="L4" s="1" t="s">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12" ht="13.550000000000001">
-      <x:c r="A5" s="6" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="s">
+      <x:c r="A5" s="7" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B5" s="7" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C5" s="7" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D5" s="12" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F5" s="7" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G5" s="6">
+      <x:c r="G5" s="7">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H5" s="4">
+      <x:c r="H5" s="5">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I5" s="4">
+      <x:c r="I5" s="5">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J5" s="4">
+      <x:c r="J5" s="5">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="L5" s="6" t="s">
-        <x:v>30</x:v>
+      <x:c r="L5" s="7" t="s">
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12" ht="13.550000000000001">
-      <x:c r="A6" s="6" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E6" s="3" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="F6" s="6" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G6" s="6">
+      <x:c r="A6" s="7" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B6" s="7" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F6" s="7" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G6" s="7">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H6" s="4">
+      <x:c r="H6" s="5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I6" s="4">
+      <x:c r="I6" s="5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J6" s="4">
+      <x:c r="J6" s="5">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="L6" s="6" t="s">
-        <x:v>26</x:v>
+      <x:c r="L6" s="7" t="s">
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12" ht="13.550000000000001">
-      <x:c r="A7" s="6" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E7" s="3" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G7" s="6">
+      <x:c r="A7" s="7" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B7" s="7" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F7" s="7" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="G7" s="7">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="4">
+      <x:c r="H7" s="5">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I7" s="4">
+      <x:c r="I7" s="5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="J7" s="4">
+      <x:c r="J7" s="5">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="L7" s="6" t="s">
-        <x:v>28</x:v>
+      <x:c r="L7" s="7" t="s">
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12" ht="13.550000000000001">
-      <x:c r="A8" s="6" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="s">
+      <x:c r="A8" s="7" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B8" s="7" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C8" s="7" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D8" s="12" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="E8" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F8" s="6" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G8" s="4">
+      <x:c r="D8" s="13" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F8" s="7" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G8" s="5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H8" s="4">
+      <x:c r="H8" s="5">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="I8" s="4">
+      <x:c r="I8" s="5">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="4">
+      <x:c r="J8" s="5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="L8" s="6" t="s">
-        <x:v>37</x:v>
+      <x:c r="L8" s="7" t="s">
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12" ht="13.550000000000001">
-      <x:c r="A9" s="6" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D9" s="12" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E9" s="3" t="s">
+      <x:c r="A9" s="7" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B9" s="7" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D9" s="13" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F9" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G9" s="5">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="F9" s="6" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G9" s="4">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H9" s="4">
+      <x:c r="H9" s="5">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I9" s="4">
+      <x:c r="I9" s="5">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="J9" s="4">
+      <x:c r="J9" s="5">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="L9" s="6" t="s">
-        <x:v>57</x:v>
+      <x:c r="L9" s="7" t="s">
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
-      <x:c r="A10" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C10" s="2" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D10" s="12" t="s">
+      <x:c r="A10" s="2" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B10" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C10" s="3" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D10" s="13" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E10" s="3" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F10" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G10" s="3">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H10" s="3">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E10" s="2" t="s">
+      <x:c r="I10" s="3">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F10" s="2" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="G10" s="2">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H10" s="2">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="I10" s="2">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J10" s="2">
+      <x:c r="J10" s="3">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L10" t="s">
-        <x:v>40</x:v>
+      <x:c r="L10" s="1" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
-      <x:c r="A11" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C11" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="12" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E11" s="2" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F11" s="2" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G11" s="2">
+      <x:c r="A11" s="2" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E11" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F11" s="3" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="G11" s="3">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H11" s="2">
+      <x:c r="H11" s="3">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="I11" s="2">
+      <x:c r="I11" s="3">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J11" s="2">
+      <x:c r="J11" s="3">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="L11" t="s">
-        <x:v>25</x:v>
+      <x:c r="L11" s="1" t="s">
+        <x:v>39</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -19,231 +19,207 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="75">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+  <x:si>
+    <x:t>Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포슬포슬 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매운 양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>호박. 씨앗으로 호박씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GrowthStageMinutesList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최소 획득개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬에 배치할 프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1152,3456,1152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>864,2592,864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최소 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1440,4320,1440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 얻는 아이템 id</x:t>
+  </x:si>
   <x:si>
     <x:t>성장 단계별 걸리는 시간 (분 단위) 864,2592,864</x:t>
   </x:si>
   <x:si>
+    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>72,144,144</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon_Crop</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3456,2304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9504,6336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4320,2880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop Item</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>576,2304,2304,576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
     <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
     <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
     <x:t>HarvestItemDataId</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Seed_Potato</x:t>
   </x:si>
   <x:si>
     <x:t>SeedDropMinCount</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>576,2304,2304,576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포슬포슬 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매운 양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Crop</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9504,6336</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3456,2304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4320,2880</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop Item</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최소 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최소 획득개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>864,2592,864</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 얻는 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씬에 배치할 프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1152,3456,1152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1440,4320,1440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMaxCount</x:t>
-  </x:si>
-  <x:si>
     <x:t>토마토. 씨앗으로 토마토씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>달달한 당근. 씨앗으로 당근씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GrowthStageMinutesList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>호박. 씨앗으로 호박씨유를 만들 수 있다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -988,140 +964,140 @@
   <x:sheetData>
     <x:row r="1" spans="1:13" customHeight="1">
       <x:c r="A1" s="9" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C1" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F1" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G1" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H1" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I1" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="J1" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K1" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="L1" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="M1" s="5"/>
     </x:row>
     <x:row r="2" spans="1:13" ht="13.550000000000001">
       <x:c r="A2" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="G2" s="4" t="str">
         <x:f>IFERROR(__xludf.DUMMYFUNCTION("AI(""표 컨텍스트를 기반으로 이 셀에 적절한 값을 입력해 줘"")"),"int")</x:f>
         <x:v>int</x:v>
       </x:c>
       <x:c r="H2" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="I2" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="J2" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="K2" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="L2" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="M2" s="5"/>
     </x:row>
     <x:row r="3" spans="1:13" ht="16.399999999999999">
       <x:c r="A3" s="8" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B3" s="10" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="C3" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D3" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E3" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G3" s="4" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B3" s="10" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="I3" s="5" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J3" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="K3" s="5" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="F3" s="4" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H3" s="5" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="I3" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="J3" s="5" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="K3" s="5" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="L3" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M3" s="5"/>
     </x:row>
     <x:row r="4" spans="1:12" ht="13.550000000000001">
       <x:c r="A4" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B4" s="7" t="s">
-        <x:v>21</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C4" s="11" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D4" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F4" s="7" t="s">
-        <x:v>37</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G4" s="7">
         <x:v>3</x:v>
@@ -1136,27 +1112,27 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K4" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="L4" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:12" ht="13.550000000000001">
       <x:c r="A5" s="7" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B5" s="7" t="s">
-        <x:v>17</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="7" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D5" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F5" s="7" t="s">
         <x:v>42</x:v>
@@ -1174,27 +1150,27 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="L5" s="7" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:12" ht="13.550000000000001">
       <x:c r="A6" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B6" s="7" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C6" s="7" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D6" s="12" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E6" s="4" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="F6" s="7" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G6" s="7">
         <x:v>2</x:v>
@@ -1209,24 +1185,24 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="L6" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:12" ht="13.550000000000001">
       <x:c r="A7" s="7" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B7" s="7" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C7" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D7" s="12" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E7" s="4" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D7" s="12" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="F7" s="7" t="s">
         <x:v>45</x:v>
@@ -1244,27 +1220,27 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L7" s="7" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:12" ht="13.550000000000001">
       <x:c r="A8" s="7" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B8" s="7" t="s">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
-        <x:v>16</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D8" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F8" s="7" t="s">
-        <x:v>40</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="G8" s="5">
         <x:v>5</x:v>
@@ -1279,27 +1255,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="7" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:12" ht="13.550000000000001">
       <x:c r="A9" s="7" t="s">
-        <x:v>68</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="7" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C9" s="7" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="D9" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F9" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G9" s="5">
         <x:v>2</x:v>
@@ -1314,27 +1290,27 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L9" s="7" t="s">
-        <x:v>68</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:12" customHeight="1">
       <x:c r="A10" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="3" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D10" s="13" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E10" s="3" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F10" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="F10" t="s">
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G10" s="3">
         <x:v>4</x:v>
@@ -1349,27 +1325,27 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:12" customHeight="1">
       <x:c r="A11" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B11" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C11" s="3" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D11" s="13" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C11" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="13" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="E11" s="3" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="F11" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F11" t="s">
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G11" s="3">
         <x:v>6</x:v>
@@ -1384,7 +1360,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -19,207 +19,243 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="79">
+  <x:si>
+    <x:t>완두콩</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>성장 단계별 걸리는 시간 (분 단위) 864,2592,864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매운 양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포슬포슬 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
   <x:si>
     <x:t>Onion</x:t>
   </x:si>
   <x:si>
-    <x:t>Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>작물설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포슬포슬 감자</x:t>
-  </x:si>
-  <x:si>
     <x:t>Potato</x:t>
   </x:si>
   <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매운 양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carrot</x:t>
+    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>576,2304,2304,576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredSeedCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3456,2304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop Item</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9504,6336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72,144,144</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4320,2880</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 얻는 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1152,3456,1152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>864,2592,864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1440,4320,1440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심을때 소모되는 씨앗 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최소 획득개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최소 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬에 배치할 프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>토마토. 씨앗으로 토마토씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달달한 당근. 씨앗으로 당근씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>호박. 씨앗으로 호박씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>GrowthStageMinutesList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최소 획득개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씬에 배치할 프리팹 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1152,3456,1152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>864,2592,864</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최소 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1440,4320,1440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 얻는 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>성장 단계별 걸리는 시간 (분 단위) 864,2592,864</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72,144,144</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon_Crop</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3456,2304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9504,6336</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4320,2880</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop Item</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>완두콩</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>576,2304,2304,576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>토마토. 씨앗으로 토마토씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달달한 당근. 씨앗으로 당근씨유를 만들 수 있다.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -307,7 +343,10 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -946,421 +985,477 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:M11"/>
+  <x:dimension ref="A1:N11"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.28515625" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="16.5703125" style="3" customWidth="1"/>
-    <x:col min="3" max="3" width="45.25" style="3" bestFit="1" customWidth="1"/>
-    <x:col min="4" max="4" width="49.8984375" style="3" bestFit="1" customWidth="1"/>
-    <x:col min="5" max="5" width="29.7265625" style="3" bestFit="1" customWidth="1"/>
-    <x:col min="6" max="6" width="24.7109375" style="3" customWidth="1"/>
-    <x:col min="7" max="7" width="20" style="3" customWidth="1"/>
-    <x:col min="8" max="9" width="25.4453125" style="3" customWidth="1"/>
-    <x:col min="10" max="11" width="19.7109375" style="3" customWidth="1"/>
-    <x:col min="12" max="12" width="21.6953125" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="13" max="13" width="17.7109375" style="3" customWidth="1"/>
+    <x:col min="1" max="1" width="14.28515625" style="3" customWidth="1"/>
+    <x:col min="2" max="2" width="16.5703125" style="4" customWidth="1"/>
+    <x:col min="3" max="3" width="45.25" style="4" bestFit="1" customWidth="1"/>
+    <x:col min="4" max="4" width="49.8984375" style="4" bestFit="1" customWidth="1"/>
+    <x:col min="5" max="5" width="27.1875" style="4" bestFit="1" customWidth="1"/>
+    <x:col min="6" max="6" width="31.67578125" style="4" bestFit="1" customWidth="1"/>
+    <x:col min="7" max="7" width="24.7109375" style="4" customWidth="1"/>
+    <x:col min="8" max="8" width="27.1875" style="4" bestFit="1" customWidth="1"/>
+    <x:col min="9" max="9" width="25.4453125" style="4" customWidth="1"/>
+    <x:col min="10" max="11" width="24.15234375" style="4" bestFit="1" customWidth="1"/>
+    <x:col min="12" max="12" width="31.3828125" style="4" bestFit="1" customWidth="1"/>
+    <x:col min="13" max="13" width="21.6953125" style="2" bestFit="1" customWidth="1"/>
+    <x:col min="14" max="14" width="17.7109375" style="4" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:13" customHeight="1">
-      <x:c r="A1" s="9" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="B1" s="4" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C1" s="5" t="s">
+    <x:row r="1" spans="1:14" customHeight="1">
+      <x:c r="A1" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B1" s="5" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C1" s="6" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D1" s="5" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D1" s="4" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="E1" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="F1" s="4" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G1" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H1" s="6" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="I1" s="5" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="J1" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="K1" s="5" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="L1" s="5" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="M1" s="5"/>
+      <x:c r="E1" s="5" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="F1" s="5" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G1" s="5" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H1" s="5" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I1" s="7" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="J1" s="6" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="K1" s="6" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="L1" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="M1" s="6" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="N1" s="6"/>
     </x:row>
-    <x:row r="2" spans="1:13" ht="13.550000000000001">
-      <x:c r="A2" s="8" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B2" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C2" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D2" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E2" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G2" s="4" t="str">
+    <x:row r="2" spans="1:14" ht="13.550000000000001">
+      <x:c r="A2" s="9" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B2" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D2" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E2" s="5" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F2" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G2" s="5" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H2" s="5" t="str">
         <x:f>IFERROR(__xludf.DUMMYFUNCTION("AI(""표 컨텍스트를 기반으로 이 셀에 적절한 값을 입력해 줘"")"),"int")</x:f>
         <x:v>int</x:v>
       </x:c>
-      <x:c r="H2" s="5" t="s">
+      <x:c r="I2" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K2" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="M2" s="6" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="N2" s="6"/>
+    </x:row>
+    <x:row r="3" spans="1:14" ht="16.399999999999999">
+      <x:c r="A3" s="9" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D3" s="5" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="E3" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F3" s="5" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="G3" s="5" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H3" s="5" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="I2" s="5" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="J2" s="5" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="K2" s="5" t="s">
+      <x:c r="K3" s="6" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="M3" s="6" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="N3" s="6"/>
+    </x:row>
+    <x:row r="4" spans="1:13" ht="13.550000000000001">
+      <x:c r="A4" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C4" s="12" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D4" s="13" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E4" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F4" s="5" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H4" s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I4" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J4" s="6">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K4" s="6">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="L4" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="M4" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:13" ht="13.550000000000001">
+      <x:c r="A5" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="8" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C5" s="8" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F5" s="5" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H5" s="8">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="I5" s="6">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="J5" s="6">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K5" s="6">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="L5" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="M5" s="8" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:13" ht="13.550000000000001">
+      <x:c r="A6" s="8" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B6" s="8" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D6" s="13" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E6" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F6" s="5" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H6" s="8">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I6" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J6" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K6" s="6">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="L6" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="M6" s="8" t="s">
+        <x:v>6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:13" ht="13.550000000000001">
+      <x:c r="A7" s="8" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="L2" s="5" t="s">
+      <x:c r="B7" s="8" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C7" s="8" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="13" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E7" s="13" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="M2" s="5"/>
+      <x:c r="H7" s="8">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I7" s="6">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J7" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K7" s="6">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="L7" s="4" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="M7" s="8" t="s">
+        <x:v>9</x:v>
+      </x:c>
     </x:row>
-    <x:row r="3" spans="1:13" ht="16.399999999999999">
-      <x:c r="A3" s="8" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="B3" s="10" t="s">
+    <x:row r="8" spans="1:13" ht="13.550000000000001">
+      <x:c r="A8" s="8" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F8" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H8" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="I8" s="6">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J8" s="6">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K8" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="L8" s="4" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="M8" s="8" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:13" ht="13.550000000000001">
+      <x:c r="A9" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B9" s="8" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C9" s="8" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D9" s="14" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="E9" s="14" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F9" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="H9" s="6">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I9" s="6">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="J9" s="6">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="K9" s="6">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="L9" s="4" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="C3" s="4" t="s">
+      <x:c r="M9" s="8" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:13" customHeight="1">
+      <x:c r="A10" s="3" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="3" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D10" s="14" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E10" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G10" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="H10" s="4">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="I10" s="4">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="J10" s="4">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K10" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L10" s="4" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="M10" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:13" customHeight="1">
+      <x:c r="A11" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B11" s="3" t="s">
         <x:v>43</x:v>
       </x:c>
-      <x:c r="D3" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="E3" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F3" s="4" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G3" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H3" s="5" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="I3" s="5" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="J3" s="5" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="K3" s="5" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="L3" s="5" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="M3" s="5"/>
-    </x:row>
-    <x:row r="4" spans="1:12" ht="13.550000000000001">
-      <x:c r="A4" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="B4" s="7" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D4" s="12" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="s">
+      <x:c r="C11" s="4" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D11" s="14" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="F4" s="7" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G4" s="7">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H4" s="5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I4" s="5">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="J4" s="5">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="K4" s="3" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="L4" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:12" ht="13.550000000000001">
-      <x:c r="A5" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B5" s="7" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="7" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D5" s="12" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F5" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="G5" s="7">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H5" s="5">
+      <x:c r="E11" s="14" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G11" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="H11" s="4">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I5" s="5">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J5" s="5">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="L5" s="7" t="s">
-        <x:v>42</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:12" ht="13.550000000000001">
-      <x:c r="A6" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="B6" s="7" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C6" s="7" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="12" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F6" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="G6" s="7">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H6" s="5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I6" s="5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J6" s="5">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="L6" s="7" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:12" ht="13.550000000000001">
-      <x:c r="A7" s="7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="B7" s="7" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C7" s="7" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D7" s="12" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F7" s="7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G7" s="7">
+      <x:c r="I11" s="4">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="J11" s="4">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K11" s="4">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H7" s="5">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I7" s="5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="J7" s="5">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="L7" s="7" t="s">
-        <x:v>45</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:12" ht="13.550000000000001">
-      <x:c r="A8" s="7" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="B8" s="7" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="7" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="13" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E8" s="4" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F8" s="7" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="G8" s="5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H8" s="5">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="I8" s="5">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J8" s="5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="L8" s="7" t="s">
-        <x:v>44</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:12" ht="13.550000000000001">
-      <x:c r="A9" s="7" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="B9" s="7" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="7" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D9" s="13" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F9" s="7" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G9" s="5">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H9" s="5">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I9" s="5">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="J9" s="5">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="L9" s="7" t="s">
-        <x:v>27</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:12" customHeight="1">
-      <x:c r="A10" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="B10" s="2" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C10" s="3" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="D10" s="13" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="E10" s="3" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="F10" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="G10" s="3">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="H10" s="3">
+      <x:c r="L11" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="M11" s="2" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="I10" s="3">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="J10" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L10" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:12" customHeight="1">
-      <x:c r="A11" s="2" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B11" s="2" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="3" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D11" s="13" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="E11" s="3" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F11" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="G11" s="3">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H11" s="3">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="I11" s="3">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="J11" s="3">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="L11" s="1" t="s">
-        <x:v>38</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/JsonConverter/ExcelFiles/CropData.xlsx
+++ b/JsonConverter/ExcelFiles/CropData.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294939905" windowHeight="17820"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="4294938660" windowHeight="16530"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="시트1" sheetId="1" r:id="rId4"/>
@@ -21,235 +21,235 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="79">
   <x:si>
+    <x:t>성장 단계별 걸리는 시간 (분 단위) 864,2592,864</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72,144,144</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop Item</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PrefabPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RequiredSeedCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedDropMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMinCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 작물 최소 획득개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최대 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SeedItemDataId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>심을때 소모되는 씨앗 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 얻는 아이템 id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Seed_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HarvestMaxCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수확시 씨앗 최소 획득 개수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씬에 배치할 프리팹 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>57,230,230,57</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이디</x:t>
+  </x:si>
+  <x:si>
     <x:t>완두콩</x:t>
   </x:si>
   <x:si>
+    <x:t>Pea</x:t>
+  </x:si>
+  <x:si>
     <x:t>int</x:t>
   </x:si>
   <x:si>
-    <x:t>성장 단계별 걸리는 시간 (분 단위) 864,2592,864</x:t>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>950,633</x:t>
+  </x:si>
+  <x:si>
+    <x:t>아이콘 경로</x:t>
+  </x:si>
+  <x:si>
+    <x:t>350,230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>매운 양파</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>작물설명</x:t>
+  </x:si>
+  <x:si>
+    <x:t>포슬포슬 감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>432,288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86,259,86</x:t>
+  </x:si>
+  <x:si>
+    <x:t>115,345,115</x:t>
+  </x:si>
+  <x:si>
+    <x:t>144,432,144</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Potato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Images/Icon_Image/lmage_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Onion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Wheat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crop_Pea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
   </x:si>
   <x:si>
     <x:t>Crop_Corn</x:t>
   </x:si>
   <x:si>
-    <x:t>Crop_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맛있는 옥수수, 씨앗으로 옥수수씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pea</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이콘 경로</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>아이디</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Images/Icon_Image/lmage_Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Seed_Tomato</x:t>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달달한 당근. 씨앗으로 당근씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>Images/Icon_Image/lmage_Pea</x:t>
   </x:si>
   <x:si>
-    <x:t>작물설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tomato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>매운 양파</x:t>
-  </x:si>
-  <x:si>
-    <x:t>포슬포슬 감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Carrot</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pumpkin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wheat</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Onion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Potato</x:t>
-  </x:si>
-  <x:si>
-    <x:t>밀. 밀씨눈유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>576,2304,2304,576</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedDropMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심을때 소모되는 씨앗 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RequiredSeedCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3456,2304</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crop Item</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9504,6336</x:t>
-  </x:si>
-  <x:si>
-    <x:t>72,144,144</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4320,2880</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PrefabPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMaxCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 얻는 아이템 id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1152,3456,1152</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SeedItemDataId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>864,2592,864</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1440,4320,1440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>심을때 소모되는 씨앗 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HarvestMinCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 작물 최소 획득개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최소 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수확시 씨앗 최대 획득 개수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씬에 배치할 프리팹 경로</x:t>
-  </x:si>
-  <x:si>
     <x:t>토마토. 씨앗으로 토마토씨유를 만들 수 있다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달달한 당근. 씨앗으로 당근씨유를 만들 수 있다.</x:t>
   </x:si>
   <x:si>
     <x:t>호박. 씨앗으로 호박씨유를 만들 수 있다.</x:t>
@@ -1005,152 +1005,152 @@
   <x:sheetData>
     <x:row r="1" spans="1:14" customHeight="1">
       <x:c r="A1" s="10" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B1" s="5" t="s">
-        <x:v>56</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D1" s="5" t="s">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E1" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F1" s="5" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G1" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H1" s="5" t="s">
-        <x:v>71</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="I1" s="7" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="J1" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K1" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="L1" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="M1" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="N1" s="6"/>
     </x:row>
     <x:row r="2" spans="1:14" ht="13.550000000000001">
       <x:c r="A2" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C2" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E2" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F2" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="G2" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H2" s="5" t="str">
         <x:f>IFERROR(__xludf.DUMMYFUNCTION("AI(""표 컨텍스트를 기반으로 이 셀에 적절한 값을 입력해 줘"")"),"int")</x:f>
         <x:v>int</x:v>
       </x:c>
       <x:c r="I2" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="J2" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="K2" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L2" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="M2" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="N2" s="6"/>
     </x:row>
     <x:row r="3" spans="1:14" ht="16.399999999999999">
       <x:c r="A3" s="9" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C3" s="5" t="s">
-        <x:v>60</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D3" s="5" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="E3" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F3" s="5" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G3" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="H3" s="5" t="s">
-        <x:v>70</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="I3" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J3" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K3" s="6" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="L3" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M3" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="N3" s="6"/>
     </x:row>
     <x:row r="4" spans="1:13" ht="13.550000000000001">
       <x:c r="A4" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C4" s="12" t="s">
-        <x:v>76</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D4" s="13" t="s">
-        <x:v>58</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E4" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F4" s="5" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G4" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="H4" s="8">
         <x:v>3</x:v>
@@ -1165,33 +1165,33 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="L4" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="M4" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:13" ht="13.550000000000001">
       <x:c r="A5" s="8" t="s">
-        <x:v>3</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B5" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C5" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D5" s="13" t="s">
-        <x:v>55</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E5" s="13" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="F5" s="5" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="F5" s="5" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="G5" s="8" t="s">
-        <x:v>3</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H5" s="8">
         <x:v>3</x:v>
@@ -1206,33 +1206,33 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="L5" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="M5" s="8" t="s">
-        <x:v>3</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:13" ht="13.550000000000001">
       <x:c r="A6" s="8" t="s">
-        <x:v>6</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B6" s="8" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C6" s="8" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="C6" s="8" t="s">
-        <x:v>39</x:v>
-      </x:c>
       <x:c r="D6" s="13" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E6" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F6" s="5" t="s">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G6" s="8" t="s">
-        <x:v>6</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H6" s="8">
         <x:v>2</x:v>
@@ -1247,33 +1247,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="L6" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="M6" s="8" t="s">
-        <x:v>6</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:13" ht="13.550000000000001">
       <x:c r="A7" s="8" t="s">
-        <x:v>9</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B7" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C7" s="8" t="s">
-        <x:v>0</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D7" s="13" t="s">
-        <x:v>67</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E7" s="13" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F7" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="G7" s="8" t="s">
-        <x:v>9</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H7" s="8">
         <x:v>10</x:v>
@@ -1288,33 +1288,33 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="L7" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="M7" s="8" t="s">
-        <x:v>9</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:13" ht="13.550000000000001">
       <x:c r="A8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C8" s="8" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D8" s="14" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E8" s="14" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D8" s="14" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E8" s="14" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F8" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H8" s="6">
         <x:v>5</x:v>
@@ -1329,33 +1329,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L8" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="M8" s="8" t="s">
-        <x:v>10</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:13" ht="13.550000000000001">
       <x:c r="A9" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C9" s="8" t="s">
         <x:v>77</x:v>
       </x:c>
       <x:c r="D9" s="14" t="s">
-        <x:v>68</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E9" s="14" t="s">
-        <x:v>23</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F9" s="5" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H9" s="6">
         <x:v>2</x:v>
@@ -1370,33 +1370,33 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="L9" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="M9" s="8" t="s">
-        <x:v>17</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:13" customHeight="1">
       <x:c r="A10" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B10" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D10" s="14" t="s">
-        <x:v>49</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E10" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H10" s="4">
         <x:v>4</x:v>
@@ -1411,33 +1411,33 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L10" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="M10" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:13" customHeight="1">
       <x:c r="A11" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B11" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D11" s="14" t="s">
-        <x:v>57</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E11" s="14" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H11" s="4">
         <x:v>6</x:v>
@@ -1452,10 +1452,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="L11" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="M11" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
